--- a/rules.xlsx
+++ b/rules.xlsx
@@ -154,7 +154,8 @@
     <t>原住民族歲時祭儀放假規定</t>
   </si>
   <si>
-    <t>依據規定，原住民族歲時祭儀為應放假之民俗節日，放假 1 日。具原住民身分之同仁，可於原民會公告之各族別放假日期內，持足資證明族別之戶籍資料向機關申請放假。</t>
+    <t>依據規定，原具原住民身分者得於其本人、其父母或配偶之所屬民族歲時祭儀放假日期中，於該年擇三日放假。具原住民身分之同仁，可於原民會公告之各族別放假日期內，持足資證明族別之戶籍資料向機關申請放假。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
   <si>
     <t>Source</t>
   </si>
@@ -42,7 +42,7 @@
     <t>事假與家庭照顧假規定</t>
   </si>
   <si>
-    <t>每年准給7日。因家庭成員預防接種或重大事故須親自照顧時，得請家庭照顧假(7日)；另有身心調適假(3日)，均併入事假計算。超過規定日數之事假，應按日扣除俸(薪)給。</t>
+    <t>每年准給7日。家庭成員須親自照顧時得請家庭照顧假(7日)；身心調適假(3日)，併入事假計算。超額扣俸。</t>
   </si>
   <si>
     <t>病假,生病,生理假</t>
@@ -51,7 +51,7 @@
     <t>病假與生理假天數</t>
   </si>
   <si>
-    <t>每年准給28日。女性公務人員因生理日致工作有困難者，每月得請生理假1日，全年請假日數未逾3日，不併入病假計算。連續請病假2日以上者，須附具合法醫療機構證明。</t>
+    <t>每年准給28日。女性每月得請生理假1日，全年未逾3日不併入病假。連續2日以上須附證明。</t>
   </si>
   <si>
     <t>喪假,死亡,過世,百日</t>
@@ -60,102 +60,232 @@
     <t>喪假核給天數與期限</t>
   </si>
   <si>
-    <t>父母、養父母、配偶死亡者，給喪假15日；繼父母、配偶之父母、配偶之養父母、子女死亡者，給喪假10日；曾祖父母、祖父母、配偶之祖父母、配偶之繼父母、兄弟姊妹死亡者，給喪假5日。喪假應於百日內請畢。</t>
+    <t>父母配偶死亡給15日；子女、配偶父母死亡給10日；祖父母、兄弟姊妹死亡給5日。百日內請畢。</t>
+  </si>
+  <si>
+    <t>婚假,結婚,登記</t>
+  </si>
+  <si>
+    <t>婚假天數與請假期限</t>
+  </si>
+  <si>
+    <t>給婚假14日，應自結婚前1個月起3個月內請畢。特殊事由核准者得於1年內請畢。</t>
+  </si>
+  <si>
+    <t>產前假,懷孕,孕婦</t>
+  </si>
+  <si>
+    <t>產前假天數與規定</t>
+  </si>
+  <si>
+    <t>懷孕者產前給產前假8日，得分次申請，不得保留至分娩後。</t>
+  </si>
+  <si>
+    <t>娩假,生產,生小孩,流產</t>
+  </si>
+  <si>
+    <t>娩假(產假)與流產假規定</t>
+  </si>
+  <si>
+    <t>分娩後給娩假42日；流產依週數給21或14日。應一次請畢。</t>
+  </si>
+  <si>
+    <t>陪產假,陪產檢,老婆懷孕</t>
+  </si>
+  <si>
+    <t>陪產檢及陪產假天數</t>
+  </si>
+  <si>
+    <t>配偶產檢或分娩，給陪產檢及陪產假7日，得分次申請。應於配偶懷孕至娩後15日內請畢。</t>
+  </si>
+  <si>
+    <t>健檢,健康檢查,公假</t>
+  </si>
+  <si>
+    <t>健康檢查公假規定</t>
+  </si>
+  <si>
+    <t>40歲以上每2年補助一次健檢並給公假1天；未滿40歲自費參加者亦給公假1天。</t>
+  </si>
+  <si>
+    <t>捐贈,骨髓,器官,捐血</t>
+  </si>
+  <si>
+    <t>捐贈骨髓或器官假別</t>
+  </si>
+  <si>
+    <t>捐贈骨髓或器官視實際需要給公假。捐血得核給公假半日。</t>
+  </si>
+  <si>
+    <t>休假,年假,級距,天數</t>
+  </si>
+  <si>
+    <t>休假天數給假級距表</t>
+  </si>
+  <si>
+    <t>滿1年給7日；滿3年14日；滿6年21日；滿9年28日；滿14年30日。</t>
   </si>
   <si>
     <t>臺東縣政府及所屬機關學校加班費支給管制要點</t>
   </si>
   <si>
-    <t>加班時數,加班上限,加班規定</t>
-  </si>
-  <si>
-    <t>臺東縣府加班時數上限規定</t>
-  </si>
-  <si>
-    <t>依據臺東縣府管制要點，一般加班時數上限：辦公日不得超過4小時，放假日不得超過8小時，每月不得超過20小時。如因業務需要專案加班，每月不得超過60小時。</t>
-  </si>
-  <si>
-    <t>補休,加班費,期限</t>
+    <t>加班時數,上限,20小時,60小時</t>
+  </si>
+  <si>
+    <t>加班時數上限規定</t>
+  </si>
+  <si>
+    <t>辦公日加班上限4小時，放假日8小時，每月不得超過20小時。專案加班上限60小時。</t>
+  </si>
+  <si>
+    <t>補休,加班費,2年期限</t>
   </si>
   <si>
     <t>加班費換算與補休期限</t>
   </si>
   <si>
-    <t>加班費計發依各機關規定基準辦理。各機關人員加班餘數合併計算後僅得選擇補休假，補休假以小時為單位，應於加班後2年內補休完畢。</t>
+    <t>加班得選擇補休，以小時為單位，應於2年內補休完畢。</t>
+  </si>
+  <si>
+    <t>臺東縣政府加強職員勤惰差假補充規定</t>
+  </si>
+  <si>
+    <t>出差,刷卡,縣外,差旅費</t>
+  </si>
+  <si>
+    <t>縣內外差勤與打卡規定</t>
+  </si>
+  <si>
+    <t>縣內出差免上午刷卡。縣外出差依標準表核給天數。</t>
+  </si>
+  <si>
+    <t>臺東縣政府彈性上下班實施要點</t>
+  </si>
+  <si>
+    <t>遲到,早退,忘記刷卡,彈性時間</t>
+  </si>
+  <si>
+    <t>彈性上下班與請假計算機制</t>
+  </si>
+  <si>
+    <t>核心上班時間不可缺勤。忘記刷卡應填證明單；遲到須依規定請假。</t>
+  </si>
+  <si>
+    <t>聘僱人員給假辦法</t>
+  </si>
+  <si>
+    <t>約聘僱,慰勞假,特休</t>
+  </si>
+  <si>
+    <t>約聘僱人員慰勞假天數</t>
+  </si>
+  <si>
+    <t>服務滿1年給7日；滿3年14日；滿5年15日；滿10年21日；滿14年28日。</t>
+  </si>
+  <si>
+    <t>公務人員考試錄取人員訓練請假注意事項</t>
+  </si>
+  <si>
+    <t>受訓,基礎訓練,實務訓練</t>
+  </si>
+  <si>
+    <t>考試錄取人員受訓期間請假限制</t>
+  </si>
+  <si>
+    <t>訓練期間請假比照請假規則，但基礎訓練缺課不得超過總時數20%。</t>
   </si>
   <si>
     <t>天然災害停止上班及上課作業辦法</t>
   </si>
   <si>
-    <t>颱風,停班,豪雨,放假</t>
+    <t>颱風假,停班停課,風力,雨量</t>
   </si>
   <si>
     <t>天然災害停班停課標準</t>
   </si>
   <si>
-    <t>依氣象預報，颱風暴風半徑於4小時內可能經過之地區，其平均風力可達7級以上或陣風可達10級以上時，或降雨量達警戒值，得由縣府發布停止上班。</t>
-  </si>
-  <si>
-    <t>聘僱人員給假辦法</t>
-  </si>
-  <si>
-    <t>約聘僱,慰勞假,特休,年假</t>
-  </si>
-  <si>
-    <t>約聘僱人員慰勞假天數</t>
-  </si>
-  <si>
-    <t>服務滿1年者，第2年起給慰勞假7日；滿3年給14日；滿5年給15日；滿10年給21日；滿14年以上給28日。</t>
-  </si>
-  <si>
-    <t>公務人員考試錄取人員訓練請假注意事項</t>
-  </si>
-  <si>
-    <t>受訓,基礎訓練,實務訓練,請假</t>
-  </si>
-  <si>
-    <t>考試錄取人員受訓期間請假限制</t>
-  </si>
-  <si>
-    <t>基礎訓練期間請假，比照公務人員請假規則辦理，但請假缺課時數不得超過訓練總時數之20%。實務訓練期間之請假，亦比照公務人員請假規則辦理。</t>
+    <t>平均風力達7級或陣風達10級以上，或雨量達警戒值，由縣府發布停止上班。</t>
+  </si>
+  <si>
+    <t>紀念日及節日實施辦法</t>
+  </si>
+  <si>
+    <t>歲時祭儀,原住民,豐年祭,祭典</t>
+  </si>
+  <si>
+    <t>原住民族歲時祭儀放假規定</t>
+  </si>
+  <si>
+    <t>原住民族歲時祭儀放假1日。具原住民身分者持證明文件向機關申請。</t>
   </si>
   <si>
     <t>公務員服務法</t>
   </si>
   <si>
-    <t>兼職,打工,外送</t>
+    <t>兼職,外送,公職,禁止</t>
   </si>
   <si>
     <t>公務員兼職相關規定</t>
   </si>
   <si>
-    <t>公務員除法令規定外，不得兼任他項公職或業務。非經服務機關（構）同意，不得兼任領證職業及其他反覆從事常態性之各項業務。</t>
-  </si>
-  <si>
-    <t>臺東縣政府加強職員勤惰差假補充規定</t>
-  </si>
-  <si>
-    <t>出差,公差,縣外出差</t>
-  </si>
-  <si>
-    <t>縣內外差勤與打卡規定</t>
-  </si>
-  <si>
-    <t>縣內出差人員免於上午到府刷卡，視實際需求覈實報支。縣外出差天數依「臺東縣政府員工出差天數核給標準表」辦理，依路程遠近與公務性質核給合理天數。</t>
-  </si>
-  <si>
-    <t>紀念日及節日實施辦法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>歲時祭儀, 原住民, 豐年祭, 祭典, 放假</t>
-  </si>
-  <si>
-    <t>原住民族歲時祭儀放假規定</t>
-  </si>
-  <si>
-    <t>依據規定，原具原住民身分者得於其本人、其父母或配偶之所屬民族歲時祭儀放假日期中，於該年擇三日放假。具原住民身分之同仁，可於原民會公告之各族別放假日期內，持足資證明族別之戶籍資料向機關申請放假。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>除法令規定外，不得兼任公職或業務。非經同意不得兼任領證職業或常態性業務。</t>
+  </si>
+  <si>
+    <t>休假天數,級距,年資,特休</t>
+  </si>
+  <si>
+    <t>休假級距：滿1年7日、3年14日、6年21日、9年28日、14年30日。</t>
+  </si>
+  <si>
+    <t>年資併計,代理教師,兵役,曾任公職</t>
+  </si>
+  <si>
+    <t>可併計休假之年資種類</t>
+  </si>
+  <si>
+    <t>可併計年資：曾任公職、服兵役、銓敘部認可之約聘僱、公立學校代課教師(須證明)。</t>
+  </si>
+  <si>
+    <t>年資銜接,中斷,當年度休假</t>
+  </si>
+  <si>
+    <t>年資銜接與不中斷之影響</t>
+  </si>
+  <si>
+    <t>年資銜接（無中斷）可合併計算。當年度可依總年資比例核給休假。</t>
+  </si>
+  <si>
+    <t>比例計算,剩餘月份,休假天數</t>
+  </si>
+  <si>
+    <t>休假比例計算公式</t>
+  </si>
+  <si>
+    <t>比例計算公式：(級距天數) x (當年剩餘在職月份 / 12)。不滿一月以一月計，餘數通常以半日計。</t>
+  </si>
+  <si>
+    <t>行政院與所屬中央及地方各機關公務人員休假改進措施</t>
+  </si>
+  <si>
+    <t>國旅卡,休假補助,10天,強制休假</t>
+  </si>
+  <si>
+    <t>休假補助(國旅卡)應休天數</t>
+  </si>
+  <si>
+    <t>當年具有10日以下休假資格者應全部休畢；10日以上者至少應休10日，始得請領國旅卡補助。</t>
+  </si>
+  <si>
+    <t>銓敘部函釋</t>
+  </si>
+  <si>
+    <t>私企年資,勞工年資,不併計</t>
+  </si>
+  <si>
+    <t>私部門(勞工)年資是否併計</t>
+  </si>
+  <si>
+    <t>私部門（一般勞工）年資，目前依法不得併計為公務人員休假年資。</t>
   </si>
 </sst>
 </file>
@@ -502,8 +632,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -563,114 +696,310 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C14" t="s">
         <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>身心調適假,心理健康,3日,事假</t>
+          <t>身心調適假,3日,小時,不影響考績</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>每年准給3日身心調適假，得以時計，毋須檢證，併入事假計算。機關不得拒絕且不得影響考績。</t>
+          <t>每年准給3日身心調適假，得以時計，毋須檢證。請假不影響考績，機關不得拒絕 。</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>扣薪事假,事假超過7日,審慎給假</t>
+          <t>扣薪事假,超過7日,先請休假補休</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>扣薪事假核給原則</t>
+          <t>扣薪事假核給審核原則</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>請事假超過7日(不含身心調適、家庭照顧假)應先請畢休假及補休，機關再就急迫性、必要性及上班日數合理性審慎決定是否核給扣薪事假。</t>
+          <t>事假超過7日應先請畢休假及補休，機關始得審酌事由之急迫性決定是否核給扣薪事假 。</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>休假年資,年資併計,軍職,民意代表,約聘僱</t>
+          <t>休假年資併計,軍職,民意代表,公費助理</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>得採計為公務人員休假年資之範圍擴大</t>
+          <t>擴大休假年資採計範圍</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>擴大採計休假年資：含軍職、公營事業/公立學校全時專任、民意代表/村里長、依法遴聘之公費助理等，均得併計為休假年資。</t>
+          <t>可併計年資包含：軍職、各種公試錄取受訓年資、公營事業、行政法人、民意代表、依法遴聘之公費助理等全時專任年資 。</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>育嬰留停,育孫留停,休假不中斷,年資銜接</t>
+          <t>育嬰留停,育孫留停,年資銜接,休假天數不中斷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>育幼留職停薪(含育孫)回職復薪休假規定</t>
+          <t>育幼及育孫留停回職復薪休假不中斷</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>養育(照顧)3足歲以下(孫)子女留職停薪，留停前後視為年資銜接，回職復薪後均依休假年資接續核給休假，無須按前一年任職月數比例計算。</t>
+          <t>養育3歲以下(孫)子女留停回職復薪後，休假年資視為銜接，直接依年資核給天數，不需按比例計算 。</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>再任,初任,轉任,休假比例計算,3日,軍職年資</t>
+          <t>再任,初任,休假計算,3日保障假,軍職併計時間</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>再任及初任公務人員休假計算與年資併計</t>
+          <t>初任與再任公務員休假計算與年資併計差異</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>【115年起休假新制】1. 初任人員(第一次考試錄取)：到職第1年(報到當年)不論有無職前年資，一律保障給予3日休假。您的軍職、約聘僱等職前年資，必須等到「明年度」才會併入計算。到職第2年，才依前一年的在職比例核給(計算式：7日 × 去年在職月數/12，若不足3日仍給3日)。 2. 再任人員(曾任公務員再回任)：到職第1年即可併計職前年資，按當年在職月數比例核給。 3. 年資銜接者(調任/轉任)：休假天數接續計算，不受影響。</t>
+          <t>1.初任人員：到職當年(第1年)不論職前年資，一律保障3日休假；軍職等年資需待『明年』才併計。2.再任人員：回職當年即可併計職前年資按比例給假 。</t>
         </is>
       </c>
     </row>
@@ -556,369 +556,369 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>病假證明,收據,診所,合法醫療機構</t>
+          <t>病假證明,收據,掛號單,診所</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>病假證明文件放寬</t>
+          <t>病假證明文件寬減(收據即可)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>請2日以上病假或安胎延長病假，可檢具「合法醫療機構或醫師證明書(含診所)」或其他證明文件(例如就診收據)。</t>
+          <t>2日以上病假可憑合法醫療機構醫師證明或『就診收據』(含診所)辦理請假 。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>公務人員請假規則(114年修訂)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國旅卡,休假補助,16000元,10日,觀光旅遊額度</t>
+          <t>安胎,病假收據,診斷證明</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>國旅卡休假補助費額度與請領方式</t>
+          <t>安胎事由請假證明放寬</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>當年具10日以上休假者，最高補助16,000元，觀光旅遊及自行運用額度各8,000元。未達10日者每日補助1,600元。</t>
+          <t>因安胎事由請2日以上假(含延長病假)，亦可憑診斷證明或就診收據辦理，不限醫院等級 。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>公務人員任用法施行細則</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>應休畢日數,未休假加班費,10日,放棄</t>
+          <t>商調,未滿6個月,同意權,過調日期</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>應休畢日數未休畢之處理</t>
+          <t>商調程序與原機關同意權規定</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>當年應休畢日數(10日)至年終未休畢者視為放棄，不得發給未休假加班費，但仍可於年終前刷卡請領休假補助。</t>
+          <t>商調函復期限為1個月。任職滿6個月後，原機關僅能決定過調日期(原則3個月，最多延3個月)，不能拒絕 。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>公務人員任用法施行細則</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國旅卡,特約商店,行動支付,電子支付,悠遊卡</t>
+          <t>商調例外,3歲子女,霸凌,性騷擾</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>行動支付/電子支付與國旅卡結合</t>
+          <t>任職未滿6個月得商調之例外情形</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>國旅卡可綁定行動支付(LINE Pay等)或電子支付(街口等)消費。但使用附加的電子票證(悠遊卡等)儲值消費不予補助。</t>
+          <t>任職未滿6個月若為親自養育3歲以下子女(調往子女居住地)、或經認定職場霸凌/性騷擾成立者，原機關不得拒絕商調 。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>天然災害停止上班及上課作業辦法</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>重大傷病,懷孕,身心障礙,自行運用額度</t>
+          <t>颱風假,退假,不計請假,退還假,扣除假紀錄</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>特殊情形(重大傷病/懷孕)之國旅卡額度調整</t>
+          <t>颱風停班期間已請假之退假處理</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>本人、配偶或直系血親因身心障礙、懷孕或重大傷病，當年確實無法參加觀光旅遊，經機關認定，補助總額均屬自行運用額度。</t>
+          <t>若已請事、病、休假，適逢颱風停班，該停班時段的請假紀錄『會自動退還』給同仁(不計入請假時數)；娩假、流產假按半日退還。但公假、延長病假遇停班，假『不會退還』 。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>天然災害停止上班及上課作業辦法</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>退休,亡故,資遣,從寬核發,未休假加班費</t>
+          <t>停班標準,居住地,工作地,停班登記</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>退休/亡故/資遣人員休假補助與未休假加班費</t>
+          <t>居住地與辦公地停班標準不一之處理</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>當年度退休、資遣、亡故者，若上班日少於應給休假日數，得從寬核發。10日休假全數發給未休假加班費(或補助費)，其餘按出勤覈實發給。</t>
+          <t>居住地或上班必經地停班，但機關所在地正常上班時，同仁得憑公告給予停班登記 。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>國民旅遊卡相關事項QA</t>
+          <t>天然災害停止上班及上課作業辦法</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>留職停薪,國旅卡,刷卡消費</t>
+          <t>天然災害,出勤加班,補休,加班費</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>留職停薪期間使用國旅卡規定</t>
+          <t>天然災害期間出勤之補償</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>留職停薪期間非現職人員，應於留停前刷卡消費。留停時卡片轉為一般信用卡無法請領補助，回職復薪後須重新通知建檔。</t>
+          <t>颱風停班期間奉派負責災情處理者，依規定核給加班費或補休 。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>各機關加班費支給辦法</t>
+          <t>國民旅遊卡相關事項QA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>加班費支給時數,上限,20小時,專案加班</t>
+          <t>國旅卡,16000元,10日應休畢,強制休假</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加班費支給時數上限及專案加班</t>
+          <t>國旅卡補助額度與應休畢日數規定</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>每人加班費支給時數上限：辦公日4小時，放假日8小時，每月20小時。因搶救災害或重大專案等，得報准支給專案加班費。</t>
+          <t>具有10日以上休假者，應休畢10日，補助16000元(觀光及自行運用各8000)。不足10日者按比例給予 [cite: 4]。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>各機關加班費支給辦法</t>
+          <t>國民旅遊卡相關事項QA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>待命,值班,值日夜,加班費換算,評價</t>
+          <t>國旅卡,行動支付,LINEPay,街口,特約商店</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>待命及值班(日夜)加班費計支</t>
+          <t>國旅卡結合行動支付消費規定</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>待命時數屬加班，每小時支給基準不得低於一般加班費之50%。各主管機關得依性質、強度訂定評價換算基準。</t>
+          <t>國旅卡可綁定行動支付(LINE Pay、街口等)至特約商店消費。但單純電子票證儲值(悠遊卡)不予補助 [cite: 4]。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>各機關加班費支給辦法</t>
+          <t>國民旅遊卡相關事項QA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>加班費,支給基準,時薪</t>
+          <t>觀光旅遊額度,自行運用額度,身心障礙懷孕例外</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加班費每小時支給基準</t>
+          <t>特種情形調整國旅卡消費額度(懷孕/身障)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>非主管：薪俸+專業加給除會240。主管：薪俸+專業加給+主管職務加給除以240。均以每小時為單位。</t>
+          <t>本人/配偶/直系血親因身心障礙、懷孕、重大傷病致無法觀光旅遊，經認定後16000元全數改為自行運用額度 [cite: 4]。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>公務員服勤實施辦法</t>
+          <t>國民旅遊卡相關事項QA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>延長辦公時數,14小時,連續3日,搶救災害</t>
+          <t>退休人員,亡故,資遣,未休假加班費從寬</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>延長辦公時數上限之例外規定</t>
+          <t>特殊離職狀況(退休亡故)之給假與補助從寬</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>搶救重大災害或緊急事件，有急迫必要且人力調度困難，得連續3日不受每日14小時上限限制，但每月仍不得超過80小時。</t>
+          <t>當年度退休、資遣或亡故者，若上班日少於應給休假日數，10日強制休假全數發給未休假加班費或補助，其餘覈實發給 [cite: 4]。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>公務員服勤實施辦法</t>
+          <t>國民旅遊卡相關事項QA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>輪班輪休人員,休息時數,11小時,更換班次</t>
+          <t>國旅卡,應休畢日數,未休畢放棄</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>輪班輪休人員之更換班次與休息規定</t>
+          <t>未休畢強制休假之補助處理</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>更換班次應有連續11小時休息，以實際下班起算。非輪班輪休人員(一般公務員)不適用此限制。</t>
+          <t>應休畢之10日休假若未休畢，不得發給未休假加班費，但仍可請領休假補助費 [cite: 4]。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>公務員服勤實施辦法</t>
+          <t>各機關加班費支給辦法</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>辦公時數跨日,跨越2日,合併計算</t>
+          <t>加班費上限,20小時,60小時,專案加班</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>辦公時間跨日之工時計算</t>
+          <t>加班費支給時數上限及專案申請</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>連續辦公跨越2日者，應合併計算為第1日之辦公時數(含正常與延長時數)。如有加班事實，按歸列之第1日待遇基準計支。</t>
+          <t>一般上限：日加班4小時、月加班20小時。因重大專案或災防得申請專案加班至60或80小時 [cite: 2, 3]。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>天然災害停止上班及上課作業辦法</t>
+          <t>各機關加班費支給辦法</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>颱風假,停班停課,不補班補課,出勤</t>
+          <t>加班費時薪,計算公式,主管加給</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>天然災害停止上班上課是否為放假及出勤</t>
+          <t>加班費每小時基準計算公式</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>天然災害停班停課係緊急應變措施，以「停止上班/上課登記」，非當然放假，不採補班補課。主管指派出勤者得發給加班費或補休。</t>
+          <t>時薪公式：(薪俸 + 專業加給 + 主管加給) / 240 [cite: 3]。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>天然災害停止上班及上課作業辦法</t>
+          <t>各機關加班費支給辦法</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>颱風假,居住地,工作地,停班標準</t>
+          <t>待命,值班,加班費換算,50%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>住所與服務機關停班標準不一之處理</t>
+          <t>待命及值班時間之加班費計支</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>居住地區或上班必經地區宣布停班，但服務機關正常上班，得給予停班登記。住所地正常但服務機關停班，亦一律停班登記。</t>
+          <t>待命、值班時間亦屬加班，支給基準由主管機關自訂，但不得低於一般加班費之50% [cite: 2, 3]。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>天然災害停止上班及上課作業辦法</t>
+          <t>公務員服勤實施辦法</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>颱風假,請假中,銷假,扣除假別</t>
+          <t>延長辦公,14小時上限,搶救災害例外</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>已請假適逢天然災害停班之扣除</t>
+          <t>每日辦公時數上限及特殊例外</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>已請事、病、休假等，適逢停班，得按時扣除請假時數(娩/流產假以半日扣除)。公假及延長病假遇停班則無需扣除。</t>
+          <t>每日辦公總時數不得超過14小時。搶救災害等緊急情況可連續3日不受此限，但每月仍受上限管制 [cite: 2]。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>天然災害停止上班及上課作業辦法</t>
+          <t>公務員服勤實施辦法</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>天然災害,差勤,加班費,補休</t>
+          <t>輪班休息,11小時,更換班次</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>天然災害期間出勤之加班或補休</t>
+          <t>輪班人員換班休息時間規定</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>未宣布停班地區奉派至已停班地區執行職務，得給加班費/補休。已出差至未停班地區，不適用停班辦法，不得補休。</t>
+          <t>輪班換班應有連續11小時休息。若因搶救災害得縮短為8小時並事後補足 [cite: 2]。</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>婚假,結婚,登記</t>
+          <t>婚假,14日,3個月內</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>婚假天數與請假期限</t>
+          <t>婚假天數與期限</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>給婚假14日，應自結婚前1個月起3個月內請畢。特殊事由核准者得於1年內請畢。</t>
+          <t>婚假14日。應自結婚前1個月至後3個月內請畢，核准後得延至1年 。</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>產前假,懷孕,孕婦</t>
+          <t>產前假,8日,分次</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>產前假天數與規定</t>
+          <t>產前假規定</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>懷孕者產前給產前假8日，得分次申請，不得保留至分娩後。</t>
+          <t>產前假8日。得分次申請，不得保留至分娩後 。</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>娩假,生產,生小孩,流產</t>
+          <t>娩假,產假,42日</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>娩假(產假)與流產假規定</t>
+          <t>娩假(產假)規定</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>分娩後給娩假42日；流產依週數給21或14日。應一次請畢。</t>
+          <t>分娩後給娩假42日。懷孕20週以上流產給流產假42日；12-20週21日；未滿12週14日 。</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陪產假,陪產檢,老婆懷孕</t>
+          <t>陪產假,陪產檢,7日</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>陪產檢及陪產假天數</t>
+          <t>陪產檢及陪產假規定</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>配偶產檢或分娩，給陪產檢及陪產假7日，得分次申請。應於配偶懷孕至娩後15日內請畢。</t>
+          <t>配偶產檢或分娩給陪產檢及陪產假7日，應於懷孕至分娩後15日內請畢 。</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>健檢,健康檢查,公假</t>
+          <t>健檢公假,40歲,1天</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40歲以上每2年補助一次健檢並給公假1天；未滿40歲自費參加者亦給公假1天。</t>
+          <t>40歲以上每2年補助一次健檢並給公假1天。未滿40歲自費受檢者亦給公假1天 。</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>捐贈,骨髓,器官,捐血</t>
+          <t>捐贈器官,骨髓,捐血,公假</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>捐贈骨髓或器官假別</t>
+          <t>器官捐贈與捐血公假</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>捐贈骨髓或器官視實際需要給公假。捐血得核給公假半日。</t>
+          <t>骨髓或器官捐贈視需要給公假。捐血得核給公假半日 。</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>歲時祭儀,原住民,豐年祭,祭典</t>
+          <t>歲時祭儀,原住民,豐年祭</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>原住民族歲時祭儀放假規定</t>
+          <t>原住民族歲時祭儀假</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>原住民族歲時祭儀放假1日。具原住民身分者持證明文件向機關申請。</t>
+          <t>原住民族歲時祭儀放假1日。具原住民身分者憑證明申請 。</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>兼職,外送,公職,禁止</t>
+          <t>兼職禁止,外送,領證職業</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>公務員兼職相關規定</t>
+          <t>公務員兼職禁止規定</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>除法令規定外，不得兼任公職或業務。非經同意不得兼任領證職業或常態性業務。</t>
+          <t>除法令規定外，不得兼任公職、領證職業或反覆從事常態性業務。非經同意不得兼職 。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>公務人員留職停薪辦法</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>育孫留職停薪,不得拒絕,3歲以下</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>育孫留職停薪新制</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>公務人員申請育孫(3歲以下)留職停薪，機關不得拒絕，且得一次申請至孫子女滿3歲止 。</t>
         </is>
       </c>
     </row>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>身心調適假,3日,小時,不影響考績</t>
+          <t>身心調適假,心理健康,3日,小時</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>每年准給3日身心調適假，得以時計，毋須檢證。請假不影響考績，機關不得拒絕 。</t>
+          <t>每年准給3日身心調適假，得以時計，毋須檢證。請假不影響考績，機關不得拒絕。</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>事假超過7日應先請畢休假及補休，機關始得審酌事由之急迫性決定是否核給扣薪事假 。</t>
+          <t>事假超過7日應先請畢休假及補休，機關始得審酌事由之急迫性決定是否核給扣薪事假。</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>休假年資併計,軍職,民意代表,公費助理</t>
+          <t>休假年資併計,軍職,約聘僱</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>可併計年資包含：軍職、各種公試錄取受訓年資、公營事業、行政法人、民意代表、依法遴聘之公費助理等全時專任年資 。</t>
+          <t>可併計年資包含：軍職、各種公試錄取受訓年資、公營事業、行政法人、民意代表、依法遴聘之公費助理等全時專任年資。</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>育嬰留停,育孫留停,年資銜接,休假天數不中斷</t>
+          <t>育嬰留停,育孫留停,年資銜接</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>養育3歲以下(孫)子女留停回職復薪後，休假年資視為銜接，直接依年資核給天數，不需按比例計算 。</t>
+          <t>養育3歲以下(孫)子女留停回職復薪後，休假年資視為銜接，直接依年資核給天數，不需按比例計算。</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>再任,初任,休假計算,3日保障假,軍職併計時間</t>
+          <t>再任,初任,休假計算,3日保障假</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.初任人員：到職當年(第1年)不論職前年資，一律保障3日休假；軍職等年資需待『明年』才併計。2.再任人員：回職當年即可併計職前年資按比例給假 。</t>
+          <t>1.初任人員：到職當年(第1年)不論職前年資，一律保障3日休假；軍職等年資需待『明年』才併計。2.再任人員：回職當年即可併計職前年資按比例給假。</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>病假證明,收據,掛號單,診所</t>
+          <t>病假證明,收據,掛號單</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>病假證明文件寬減(收據即可)</t>
+          <t>病假證明文件寬減</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2日以上病假可憑合法醫療機構醫師證明或『就診收據』(含診所)辦理請假 。</t>
+          <t>2日以上病假可憑合法醫療機構醫師證明或『就診收據』(含診所)辦理請假。</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>因安胎事由請2日以上假(含延長病假)，亦可憑診斷證明或就診收據辦理，不限醫院等級 。</t>
+          <t>因安胎事由請2日以上假(含延長病假)，亦可憑診斷證明或就診收據辦理，不限醫院等級。</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>商調,未滿6個月,同意權,過調日期</t>
+          <t>商調,未滿6個月,同意權</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>商調函復期限為1個月。任職滿6個月後，原機關僅能決定過調日期(原則3個月，最多延3個月)，不能拒絕 。</t>
+          <t>商調函復期限為1個月。任職滿6個月後，原機關僅能決定過調日期(原則3個月，最多延3個月)，不能拒絕。</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>商調例外,3歲子女,霸凌,性騷擾</t>
+          <t>商調例外,3歲子女,霸凌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>任職未滿6個月若為親自養育3歲以下子女(調往子女居住地)、或經認定職場霸凌/性騷擾成立者，原機關不得拒絕商調 。</t>
+          <t>任職未滿6個月若為親自養育3歲以下子女、或經認定職場霸凌/性騷擾成立者，原機關不得拒絕商調。</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>颱風假,退假,不計請假,退還假,扣除假紀錄</t>
+          <t>颱風假,退假,不計請假,退還假</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>若已請事、病、休假，適逢颱風停班，該停班時段的請假紀錄『會自動退還』給同仁(不計入請假時數)；娩假、流產假按半日退還。但公假、延長病假遇停班，假『不會退還』 。</t>
+          <t>若已請事、病、休假，適逢颱風停班，該停班時段的假『會退還』給同仁，不計入請假時數。但公假、延長病假遇停班，假『不會退還』。</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>停班標準,居住地,工作地,停班登記</t>
+          <t>停班標準,居住地,工作地</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>居住地或上班必經地停班，但機關所在地正常上班時，同仁得憑公告給予停班登記 。</t>
+          <t>居住地或上班必經地停班，但機關所在地正常上班時，同仁得憑公告給予停班登記。</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>天然災害,出勤加班,補休,加班費</t>
+          <t>天然災害,出勤加班,補休</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>颱風停班期間奉派負責災情處理者，依規定核給加班費或補休 。</t>
+          <t>颱風停班期間奉派負責災情處理者，依規定核給加班費或補休。</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國旅卡,16000元,10日應休畢,強制休假</t>
+          <t>國旅卡,16000元,10日應休畢</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>具有10日以上休假者，應休畢10日，補助16000元(觀光及自行運用各8000)。不足10日者按比例給予 [cite: 4]。</t>
+          <t>具有10日以上休假者，應休畢10日，補助16000元。不足10日者按比例給予。</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國旅卡,行動支付,LINEPay,街口,特約商店</t>
+          <t>國旅卡,行動支付,LINEPay,街口</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>國旅卡可綁定行動支付(LINE Pay、街口等)至特約商店消費。但單純電子票證儲值(悠遊卡)不予補助 [cite: 4]。</t>
+          <t>國旅卡可綁定行動支付(LINE Pay、街口等)至特約商店消費。</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>觀光旅遊額度,自行運用額度,身心障礙懷孕例外</t>
+          <t>觀光旅遊額度,自行運用額度</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>特種情形調整國旅卡消費額度(懷孕/身障)</t>
+          <t>特種情形調整國旅卡消費額度</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>本人/配偶/直系血親因身心障礙、懷孕、重大傷病致無法觀光旅遊，經認定後16000元全數改為自行運用額度 [cite: 4]。</t>
+          <t>本人/配偶/直系血親因身心障礙、懷孕、重大傷病致無法觀光旅遊，16000元全數改為自行運用額度。</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>退休人員,亡故,資遣,未休假加班費從寬</t>
+          <t>退休人員,亡故,資遣,未休假加班費</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>當年度退休、資遣或亡故者，若上班日少於應給休假日數，10日強制休假全數發給未休假加班費或補助，其餘覈實發給 [cite: 4]。</t>
+          <t>當年度退休、資遣或亡故者，10日強制休假全數發給未休假加班費或補助，其餘覈實發給。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>應休畢之10日休假若未休畢，不得發給未休假加班費，但仍可請領休假補助費 [cite: 4]。</t>
+          <t>應休畢之10日休假若未休畢，不得發給未休假加班費，但仍可請領休假補助費。</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>加班費上限,20小時,60小時,專案加班</t>
+          <t>加班費上限,20小時,60小時</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>一般上限：日加班4小時、月加班20小時。因重大專案或災防得申請專案加班至60或80小時 [cite: 2, 3]。</t>
+          <t>一般上限：日加班4小時、月加班20小時。因重大專案或災防得申請專案加班至60或80小時。</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>加班費時薪,計算公式,主管加給</t>
+          <t>加班費時薪,計算公式</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>時薪公式：(薪俸 + 專業加給 + 主管加給) / 240 [cite: 3]。</t>
+          <t>時薪公式：(薪俸 + 專業加給 + 主管加給) / 240。</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>待命,值班,加班費換算,50%</t>
+          <t>待命,值班,50%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>待命、值班時間亦屬加班，支給基準由主管機關自訂，但不得低於一般加班費之50% [cite: 2, 3]。</t>
+          <t>待命、值班時間加班費支給基準由主管機關自訂，但不得低於一般加班費之50%。</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>延長辦公,14小時上限,搶救災害例外</t>
+          <t>延長辦公,14小時上限,搶救災害</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>每日辦公總時數不得超過14小時。搶救災害等緊急情況可連續3日不受此限，但每月仍受上限管制 [cite: 2]。</t>
+          <t>每日辦公總時數不得超過14小時。搶救災害等緊急情況可連續3日不受此限。</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>輪班換班應有連續11小時休息。若因搶救災害得縮短為8小時並事後補足 [cite: 2]。</t>
+          <t>輪班換班應有連續11小時休息。若因搶救災害得縮短為8小時並事後補足。</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>婚假14日。應自結婚前1個月至後3個月內請畢，核准後得延至1年 。</t>
+          <t>婚假14日。應自結婚前1個月至後3個月內請畢，核准後得延至1年。</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>產前假,8日,分次</t>
+          <t>產前假,8日</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>產前假8日。得分次申請，不得保留至分娩後 。</t>
+          <t>產前假8日。得分次申請，不得保留至分娩後。</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>分娩後給娩假42日。懷孕20週以上流產給流產假42日；12-20週21日；未滿12週14日 。</t>
+          <t>分娩後給娩假42日。懷孕20週以上流產給流產假42日；12-20週21日；未滿12週14日。</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>配偶產檢或分娩給陪產檢及陪產假7日，應於懷孕至分娩後15日內請畢 。</t>
+          <t>配偶產檢或分娩給陪產檢及陪產假7日，應於懷孕至分娩後15日內請畢。</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40歲以上每2年補助一次健檢並給公假1天。未滿40歲自費受檢者亦給公假1天 。</t>
+          <t>40歲以上每2年補助一次健檢並給公假1天。未滿40歲自費受檢者亦給公假1天。</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>骨髓或器官捐贈視需要給公假。捐血得核給公假半日 。</t>
+          <t>骨髓或器官捐贈視需要給公假。捐血得核給公假半日。</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>歲時祭儀,原住民,豐年祭</t>
+          <t>歲時祭儀,原住民,3天,3日,豐年祭</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>原住民族歲時祭儀假</t>
+          <t>原住民族歲時祭儀假(3日)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>原住民族歲時祭儀放假1日。具原住民身分者憑證明申請 。</t>
+          <t>【最新規定】依據修正後之《紀念日及節日實施辦法》，原住民族歲時祭儀放假天數已由1日改為3日。具原住民身分之同仁，於原民會公告之各族別歲時祭儀期間，可向機關申請放假3日。</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>除法令規定外，不得兼任公職、領證職業或反覆從事常態性業務。非經同意不得兼職 。</t>
+          <t>除法令規定外，不得兼任公職、領證職業或常態性業務。非經同意不得兼職。</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>育孫留職停薪,不得拒絕,3歲以下</t>
+          <t>育孫留職停薪,不得拒絕</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>公務人員申請育孫(3歲以下)留職停薪，機關不得拒絕，且得一次申請至孫子女滿3歲止 。</t>
+          <t>公務人員申請育孫(3歲以下)留職停薪，機關不得拒絕，且得一次申請至孫子女滿3歲止。</t>
         </is>
       </c>
     </row>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>歲時祭儀,原住民,3天,3日,豐年祭</t>
+          <t>歲時祭儀,原住民,3天,3日,豐年祭,超過日數,休假,事假</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>原住民族歲時祭儀假(3日)</t>
+          <t>原住民族歲時祭儀假(3日)與超過日數處理</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>【最新規定】依據修正後之《紀念日及節日實施辦法》，原住民族歲時祭儀放假天數已由1日改為3日。具原住民身分之同仁，於原民會公告之各族別歲時祭儀期間，可向機關申請放假3日。</t>
+          <t>【最新規定】原住民族歲時祭儀放假天數為3日。具原住民身分之同仁，於原民會公告期間可向機關申請放假3日。若因返鄉路程或實際需求，請假天數『超過』法定的3日，超過的部分可依規定請個人的『休假』或『事假』辦理。</t>
         </is>
       </c>
     </row>
